--- a/content/post/drafts/season-prediction/ladies_odds.xlsx
+++ b/content/post/drafts/season-prediction/ladies_odds.xlsx
@@ -35,10 +35,10 @@
     <t xml:space="preserve">USA</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-982</t>
+    <t xml:space="preserve">90.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-949</t>
   </si>
   <si>
     <t xml:space="preserve">Kerttu Niskanen</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">Finland</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1304</t>
+    <t xml:space="preserve">7.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1240</t>
   </si>
   <si>
     <t xml:space="preserve">Rosie Brennan</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">0.8%</t>
   </si>
   <si>
-    <t xml:space="preserve">+12095</t>
+    <t xml:space="preserve">+11948</t>
   </si>
   <si>
     <t xml:space="preserve">Linn Svahn</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">Sweden</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+16029</t>
+    <t xml:space="preserve">0.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+18419</t>
   </si>
   <si>
     <t xml:space="preserve">Jonna Sundling</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">0.4%</t>
   </si>
   <si>
-    <t xml:space="preserve">+24900</t>
+    <t xml:space="preserve">+24290</t>
   </si>
   <si>
     <t xml:space="preserve">Frida Karlsson</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">0.3%</t>
   </si>
   <si>
-    <t xml:space="preserve">+35614</t>
+    <t xml:space="preserve">+34383</t>
   </si>
 </sst>
 </file>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -463,7 +463,7 @@
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>14.04</v>
+        <v>13.4</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -480,7 +480,7 @@
         <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>121.95</v>
+        <v>120.48</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
@@ -497,7 +497,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>161.29</v>
+        <v>185.19</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
@@ -514,7 +514,7 @@
         <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>250</v>
+        <v>243.9</v>
       </c>
       <c r="E6" t="s">
         <v>22</v>
@@ -531,7 +531,7 @@
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>357.14</v>
+        <v>344.83</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
